--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-11T16:07:52+00:00</t>
+    <t>2026-03-13T19:21:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-13T19:21:03+00:00</t>
+    <t>2026-03-17T13:04:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-17T13:04:13+00:00</t>
+    <t>2026-03-18T17:17:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-18T17:17:44+00:00</t>
+    <t>2026-03-19T09:35:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T09:35:09+00:00</t>
+    <t>2026-06-08T15:24:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-08T15:24:46+00:00</t>
+    <t>2026-06-09T07:55:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T07:55:39+00:00</t>
+    <t>2026-06-09T09:58:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T09:58:53+00:00</t>
+    <t>2026-06-10T14:13:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T14:13:27+00:00</t>
+    <t>2026-06-12T15:13:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T15:13:13+00:00</t>
+    <t>2026-06-15T13:25:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T13:25:13+00:00</t>
+    <t>2026-06-16T07:36:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:36:31+00:00</t>
+    <t>2026-06-16T07:55:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T07:55:16+00:00</t>
+    <t>2026-06-16T08:15:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -79,7 +79,7 @@
     <t>Jurisdiction</t>
   </si>
   <si>
-    <t>France</t>
+    <t>France (la)</t>
   </si>
   <si>
     <t>Description</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T08:15:37+00:00</t>
+    <t>2026-06-17T09:17:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:17:48+00:00</t>
+    <t>2026-06-17T09:36:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T09:36:47+00:00</t>
+    <t>2026-06-19T10:27:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T10:27:30+00:00</t>
+    <t>2026-06-22T09:32:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:32:11+00:00</t>
+    <t>2026-06-24T08:54:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T08:54:25+00:00</t>
+    <t>2026-06-24T09:36:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T09:36:36+00:00</t>
+    <t>2026-06-24T12:11:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:11:25+00:00</t>
+    <t>2026-06-24T12:16:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-24T12:16:25+00:00</t>
+    <t>2026-06-25T08:27:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T08:27:57+00:00</t>
+    <t>2026-06-25T09:12:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:12:27+00:00</t>
+    <t>2026-06-25T09:43:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T09:43:13+00:00</t>
+    <t>2026-06-25T10:03:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:03:25+00:00</t>
+    <t>2026-06-25T10:20:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T10:20:08+00:00</t>
+    <t>2026-06-25T14:41:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
+++ b/450-contenu-fhir---ajout-des-objets-demandeorientation-decision-droitprestation/ig/ValueSet-tddui-care-plan-supporting-info.xlsx
@@ -31,7 +31,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.3.0-ballot</t>
+    <t>2.3.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-25T14:41:02+00:00</t>
+    <t>2026-06-30T07:08:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
